--- a/mode_docx_gen/pmi_mtz/part/lvttoc/ptoc1/PTOC1.xlsx
+++ b/mode_docx_gen/pmi_mtz/part/lvttoc/ptoc1/PTOC1.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="23901"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\www_obj\mode_docx_gen\part\lvttoc\ptoc1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\www5\mode_docx_gen\pmi_mtz\part\lvttoc\ptoc1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{459509AF-035D-489C-8936-8E27E70E24C0}" xr6:coauthVersionLast="46" xr6:coauthVersionMax="46" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6210" yWindow="3855" windowWidth="17700" windowHeight="15345" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6210" yWindow="3855" windowWidth="17700" windowHeight="15345"/>
   </bookViews>
   <sheets>
     <sheet name="Signals" sheetId="1" r:id="rId1"/>
@@ -356,9 +355,6 @@
     <t>Контр_СВ</t>
   </si>
   <si>
-    <t>0 - Не предусмотрено, 1 - Блокировка ступени при включенном СВ, 3 -  Блокировка ступени при отключенном СВ</t>
-  </si>
-  <si>
     <t>Пуск ф.А</t>
   </si>
   <si>
@@ -446,12 +442,15 @@
   </si>
   <si>
     <t>Icoarse</t>
+  </si>
+  <si>
+    <t>0 - Не предусмотрено, 1 - Блокировка ступени при включенном СВ, 2 -  Блокировка ступени при отключенном СВ</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -836,7 +835,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AE24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -845,7 +844,7 @@
     <col min="3" max="3" width="42.5703125" style="2" customWidth="1"/>
     <col min="4" max="4" width="20.42578125" style="2" customWidth="1"/>
     <col min="5" max="5" width="16.85546875" style="2" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" style="2" customWidth="1"/>
+    <col min="6" max="6" width="83.140625" style="2" customWidth="1"/>
     <col min="7" max="12" width="9.140625" style="2"/>
     <col min="13" max="13" width="14.7109375" style="2" customWidth="1"/>
     <col min="14" max="26" width="9.140625" style="2"/>
@@ -948,7 +947,7 @@
         <v>29</v>
       </c>
       <c r="AE1" s="2" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="2" spans="1:31" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -956,7 +955,7 @@
         <v>30</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>76</v>
@@ -1048,7 +1047,7 @@
         <v>30</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>78</v>
@@ -1140,7 +1139,7 @@
         <v>30</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>37</v>
@@ -1232,7 +1231,7 @@
         <v>30</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>47</v>
@@ -1324,16 +1323,16 @@
         <v>30</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="F6" s="3" t="s">
         <v>31</v>
@@ -1416,16 +1415,16 @@
         <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="F7" s="3" t="s">
         <v>31</v>
@@ -1508,16 +1507,16 @@
         <v>30</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>31</v>
@@ -1600,16 +1599,16 @@
         <v>30</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="F9" s="3" t="s">
         <v>31</v>
@@ -1692,16 +1691,16 @@
         <v>30</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="F10" s="3" t="s">
         <v>31</v>
@@ -1784,16 +1783,16 @@
         <v>30</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="F11" s="3" t="s">
         <v>31</v>
@@ -1876,7 +1875,7 @@
         <v>30</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>61</v>
@@ -1968,7 +1967,7 @@
         <v>30</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>70</v>
@@ -2060,7 +2059,7 @@
         <v>30</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>73</v>
@@ -2152,7 +2151,7 @@
         <v>33</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C15" s="2" t="s">
         <v>35</v>
@@ -2244,7 +2243,7 @@
         <v>33</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>85</v>
@@ -2331,7 +2330,7 @@
         <v>31</v>
       </c>
       <c r="AE16" s="2" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="17" spans="1:31" s="5" customFormat="1" x14ac:dyDescent="0.25">
@@ -2339,13 +2338,13 @@
         <v>33</v>
       </c>
       <c r="B17" s="5" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C17" s="5" t="s">
         <v>91</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="E17" s="5" t="s">
         <v>93</v>
@@ -2426,7 +2425,7 @@
         <v>31</v>
       </c>
       <c r="AE17" s="5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="18" spans="1:31" x14ac:dyDescent="0.25">
@@ -2434,7 +2433,7 @@
         <v>33</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C18" s="2" t="s">
         <v>101</v>
@@ -2446,7 +2445,7 @@
         <v>100</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>32</v>
@@ -2526,7 +2525,7 @@
         <v>33</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>66</v>
@@ -2618,7 +2617,7 @@
         <v>33</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C20" s="2" t="s">
         <v>104</v>
@@ -2630,7 +2629,7 @@
         <v>103</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>32</v>
@@ -2704,13 +2703,13 @@
         <v>33</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>106</v>
@@ -2782,7 +2781,7 @@
         <v>89</v>
       </c>
       <c r="AB21" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="22" spans="1:31" x14ac:dyDescent="0.25">
@@ -2790,13 +2789,13 @@
         <v>33</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>108</v>
@@ -2868,7 +2867,7 @@
         <v>89</v>
       </c>
       <c r="AB22" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.25">
@@ -2876,7 +2875,7 @@
         <v>33</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>109</v>
@@ -2885,10 +2884,10 @@
         <v>110</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>111</v>
+        <v>140</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>32</v>
@@ -2962,7 +2961,7 @@
         <v>33</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>86</v>
@@ -3053,7 +3052,7 @@
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:AD24">
+  <sortState ref="A2:AD24">
     <sortCondition ref="A1"/>
   </sortState>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3062,7 +3061,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:B6"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -3100,15 +3099,15 @@
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B6">
         <v>100</v>
